--- a/career-intelligence/resources/search-log-template.xlsx
+++ b/career-intelligence/resources/search-log-template.xlsx
@@ -20,27 +20,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">Week 4  ·  Search Strategy Log</t>
   </si>
   <si>
-    <t xml:space="preserve">One variable this week: geography. Fill in the setup, log 10 applications in region A and 10 in region B, then reflect. A “no” or silence is data, not failure.</t>
+    <t xml:space="preserve">One variable this week: your bet (geography or sector). Fill in the setup, log 10 in group A (your default) and 10 in group B (your bet), then reflect. A “no” or silence is data, not failure.</t>
   </si>
   <si>
     <t xml:space="preserve">MY SETUP</t>
   </si>
   <si>
-    <t xml:space="preserve">My geography bet (one line)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region A  ·  control (the region I'd default to)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region B  ·  experimental (a region I have ties to)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why I win in B (I'm local, or a sector unique to that region fits me)</t>
+    <t xml:space="preserve">My bet (one line)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bet type (geography or sector)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group A  ·  control (my default)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group B  ·  experimental (my bet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why I win in B (a region I have ties to, or an industry where I'm a strong fit)</t>
   </si>
   <si>
     <t xml:space="preserve">My skill-to-learn (the tool/process that keeps showing up)</t>
@@ -91,7 +94,7 @@
     <t xml:space="preserve">silence</t>
   </si>
   <si>
-    <t xml:space="preserve">region-unique sector; led with my pipeline</t>
+    <t xml:space="preserve">sector bet; led with my pipeline</t>
   </si>
   <si>
     <t xml:space="preserve">← example (delete)</t>
@@ -633,7 +636,7 @@
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
@@ -684,34 +687,34 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -735,80 +738,82 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9" t="str">
-        <f aca="false">"A logged: "&amp;COUNTIF(A14:A60,"A")</f>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9" t="str">
+        <f aca="false">"A logged: "&amp;COUNTIF(A15:A60,"A")</f>
         <v>A logged: 0</v>
       </c>
-      <c r="G12" s="10" t="str">
-        <f aca="false">"B logged: "&amp;COUNTIF(A14:A60,"B")</f>
+      <c r="G13" s="10" t="str">
+        <f aca="false">"B logged: "&amp;COUNTIF(A15:A60,"B")</f>
         <v>B logged: 1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="11" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="B14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="C14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="12" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="B15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="E15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="F15" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="G15" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="H15" s="13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14"/>
@@ -1035,14 +1040,14 @@
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
     </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -1053,7 +1058,7 @@
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1064,7 +1069,7 @@
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -1074,7 +1079,7 @@
       <c r="G45" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B5:G5"/>
@@ -1083,17 +1088,18 @@
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B10:G10"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B43:G43"/>
     <mergeCell ref="B44:G44"/>
     <mergeCell ref="B45:G45"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A14:A40" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A15:A40" type="list">
       <formula1>"A,B"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F14:F40" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F15:F40" type="list">
       <formula1>"reply,screen,silence,no,offer"</formula1>
       <formula2>0</formula2>
     </dataValidation>
